--- a/revit/ArmadoMuros_Insurgentes/Armado muros (todos los niveles).xlsx
+++ b/revit/ArmadoMuros_Insurgentes/Armado muros (todos los niveles).xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4268,6 +4268,982 @@
       <c r="O61" s="2" t="inlineStr">
         <is>
           <t>Plano: MURO M-27 N7-ROOF; Geometría (muros/longitudes/alto) tomada de N2, solo referencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-1</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>22#6 200 5E+1G@15</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>40#6 200/200 10E@15</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. En el detalle: 22#6 5E+1G Lb 200, 40#6 10E Lb 200 (dos cotas de 200), ramas de 6#4 1E+1G Lb 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-8</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>8#4 40 2E@15</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Ambos extremos 8#4 2E; cotas 40 y 30 en cada extremo: se tomó Lb 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-10</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>8#4 30 2E@15</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Dos dibujos: extremos 6#4 1E+1G y uno 8#4 2E, todos Lb 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-11 Nivel -2.65</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>12#4 100 3E@15</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>14#4 100 3E+1G@15</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Extremos distintos 12#4 3E / 14#4 3E+1G (Lb 100); el 22#6 5E Lb 185 del detalle es de otro muro</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-12 Nivel -2.65</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>8#4 60 2E@15</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>10#4 60/40 2E+1G@15</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. 10#4 2E+1G con cotas 60 y 40 (esquina); otro extremo 8#4 2E Lb 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-13 Nivel -2.65</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>12#4 100 3E@15</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>16#4 100 3E+2G@15</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Extremos 16#4 3E+2G / 12#4 3E (Lb 100); ramas: 8#4 2E Lb 60 y 6#4 1E Lb 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-14</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>14#4 120 3E+1G@15</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Ambos extremos 14#4 3E+1G Lb 120; el 22#6 5E+1G Lb 200 del detalle es de la esquina con otro muro</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-15</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>14#6+2#4 120 4E@15</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>32#6 200/120 8E@15</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. 14#6+2#4 4E Lb 120; 32#6 8E con cotas 120 y 200 (esquina); rama 6#4 1E+1G Lb 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-28</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>16#4 100 3E+2G@15</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Ambos extremos 16#4 3E+2G Lb 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-29</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>14#4 100 3E+1G@15</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>12#4 100/60 2E+1G@15</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. 12#4 2E+1G Lb 100 junto a cotas 60 (esquina con M-1); 14#4 3E+1G Lb 100; rama 6#4 1E+1G Lb 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-30</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>8#4 60 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>8#4 60 2E@15</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Ambos extremos 8#4 1E+1G Lb 60; rama 8#4 2E Lb 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-31</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>8#4 30 2E@15</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Detalle "M-31 Y M-33": 8#4 2E y 6#4 1E+1G, Lb 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-31A</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E@15</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>8#4 30 2E@15</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Detalle "M-31A Y M-33": 8#4 2E y 6#4 1E, Lb 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-32</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>6#4 40 1E@15</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>6#4 40 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Extremos 6#4 1E+1G / 6#4 1E, Lb 40; rama 8#4 2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-33</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>8#4 30 2E@15</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="n"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Aparece en "M-31 Y M-33" (6#4 1E+1G) y "M-31A Y M-33" (6#4 1E): se tomó 1E+1G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-33A</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>6#6 30 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="n"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="n"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Detalle "M-36 Y M-33A": 6#6 1E+1G Lb 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-34</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>6#4 40 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Ambos extremos 6#4 1E+1G Lb 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-35</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E@15</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E+1G@15</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="n"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Extremos 6#4 1E+1G / 6#4 1E, Lb 30; rama 6#6 1E+1G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>+30.55</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Muro M-36</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>6#4 30 1E@15</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>8#6 30 2E@15</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @15</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Azotea (ROOF-TECHOS, +30.55), leída del DWG: extremos asignados por la posición de las etiquetas, REVISAR en el reporte. Detalle "M-36 Y M-33A": 6#4 1E y 8#6 2E, Lb 30</t>
         </is>
       </c>
     </row>
@@ -4845,7 +5821,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Muros de azotea ("ROOF - TECHOS", arrancan en Roof N10 +30.55). Datos leídos del DWG Muros_I121, SIN asignar a extremos: pasar a la hoja Armado cuando la azotea esté modelada. El botón no lee esta hoja.</t>
+          <t>Datos de azotea leídos del DWG (referencia). YA PASADOS a la hoja Armado (filas +30.55). El botón no lee esta hoja.</t>
         </is>
       </c>
     </row>

--- a/revit/ArmadoMuros_Insurgentes/Armado muros (todos los niveles).xlsx
+++ b/revit/ArmadoMuros_Insurgentes/Armado muros (todos los niveles).xlsx
@@ -5259,7 +5259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5609,6 +5609,23 @@
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>{muro} = M-1; {elev} = +16.10; {nivel} = nombre del nivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Nivel del acero</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Superior</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Superior = el acero pertenece al nivel de arriba del entrepiso (muros de +4.70 a +7.55 -&gt; +7.55); Base = nivel de arranque</t>
         </is>
       </c>
     </row>
